--- a/docs/Dream-Drive-Functionality-Tracker.xlsx
+++ b/docs/Dream-Drive-Functionality-Tracker.xlsx
@@ -39,7 +39,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FE Web Account'!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'FE Web Public'!$A$4:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FE Admin'!$A$4:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FE Admin'!$A$4:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FE Mobile'!$A$4:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'00 Summary'!$A$4:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'01 Auth &amp; Security'!$A$4:$H$21</definedName>
@@ -49,7 +49,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'05 Booking Engine'!$A$4:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'06 Payments'!$A$4:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'07 Subscription'!$A$4:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'08 Airport &amp; Packages'!$A$4:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'08 Airport &amp; Packages'!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'09 KYC &amp; Documents'!$A$4:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'10 Agreement &amp; eSign'!$A$4:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'11 Fleet'!$A$4:$H$12</definedName>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,6 +228,9 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -253,15 +256,15 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,7 +888,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B942"/>
+    <tabColor rgb="00006100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -910,16 +913,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: catalog    |    Priority: P0    |    Overall status: In Progress</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Service: catalog    |    Priority: P0    |    Overall status: Done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Public search, car detail, availability, pricing CRUD, HOLD reserve/release/confirm, and the worker HOLD sweeper are implemented. Search UI is /fleet. Seasonal pricing and a hard DB lock against double-book are still open.</t>
+          <t>Public search, car detail calendar, availability, seasonal pricing, buffer settings, vehicle blocks, HOLD reserve/release/confirm with a serializable lock, and the worker HOLD sweeper.</t>
         </is>
       </c>
     </row>
@@ -983,7 +986,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/public/search filters city, seats, fuel, transmission, price, rentalType; returns from-price + available flag.</t>
+          <t>GET /v1/public/search filters city, type, seats, fuel, transmission, price, rentalType; sorts featured/price/popularity; returns from-price + available flag.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -991,7 +994,7 @@
           <t>GET /v1/public/search · catalog.service.ts search</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>No popularity sort; unpublished models excluded.</t>
+          <t>Unpublished models excluded. Past dates and max rental length rejected.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1028,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/public/cars/:slug with images, pricing, city.</t>
+          <t>GET /v1/public/cars/:slug with images, pricing, city. Calendar of busy days on CarDetail.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -1033,7 +1036,7 @@
           <t>GET /v1/public/cars/:slug · CarDetail.jsx</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1043,11 +1046,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Calendar of blocked dates is thin.</t>
-        </is>
-      </c>
+      <c r="H6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -1067,7 +1066,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/public/cars/:id/availability uses buffer hours and free-vehicle search.</t>
+          <t>GET /v1/public/cars/:id/availability uses buffer hours, free-vehicle search, and month busyDays.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1075,7 +1074,7 @@
           <t>GET /v1/public/cars/:id/availability</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1105,7 +1104,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>vehicleBusy checks blocking booking statuses, AvailabilityBlock, MaintenanceJob. Buffer default 3h (BUFFER_HOURS).</t>
+          <t>vehicleBusy checks blocking booking statuses, AvailabilityBlock, MaintenanceJob. Buffer from CatalogSettings (default 3h).</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -1113,7 +1112,7 @@
           <t>catalog.service.ts vehicleBusy · findFreeVehicle</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1125,7 +1124,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>No SELECT FOR UPDATE / serializable tx — race possible under concurrent checkout.</t>
+          <t>Serializable tx + SELECT FOR UPDATE on reserve.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1154,7 @@
           <t>POST /internal/availability/reserve|release|confirm</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1197,7 +1196,7 @@
           <t>apps/worker hold-sweeper.job.ts · POST /internal/holds/expire</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1231,7 +1230,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH/DELETE /v1/admin/car-models. Admin /cars page.</t>
+          <t>GET/POST/PATCH/DELETE /v1/admin/car-models with images, published, featured. Admin /cars page.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1239,9 +1238,9 @@
           <t xml:space="preserve"> /v1/admin/car-models · apps/admin/app/cars</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1249,11 +1248,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Image management is create-time only.</t>
-        </is>
-      </c>
+      <c r="H11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -1273,7 +1268,7 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>GET/POST/PUT/DELETE /v1/admin/pricing-rules (daily/hourly/extraKm/deposit).</t>
+          <t>GET/POST/PUT/DELETE /v1/admin/pricing-rules (daily/hourly/extraKm/deposit + seasonal startsOn/endsOn).</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -1281,7 +1276,7 @@
           <t xml:space="preserve"> /v1/admin/pricing-rules</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1291,11 +1286,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>No seasonal / date-window rules.</t>
-        </is>
-      </c>
+      <c r="H12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1315,7 +1306,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>/fleet uses new Search.jsx against the API (old /cars carousel still ported).</t>
+          <t>/fleet Search.jsx + /cars redirect. Home search bar. Type filter and price/popularity sort.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1323,9 +1314,9 @@
           <t>apps/web/src/ms/pages/Search.jsx</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1333,11 +1324,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Unify /cars vs /fleet; add sort chips.</t>
-        </is>
-      </c>
+      <c r="H13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -1357,17 +1344,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>featured + displayOrder on CarModel only.</t>
+          <t>featured + displayOrder on CarModel. Date-ranged PricingRule.startsOn/endsOn applied at search and quote.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CarModel.featured</t>
+          <t>CatalogSettings · PricingRule</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1375,11 +1362,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Add date-ranged PricingRule.</t>
-        </is>
-      </c>
+      <c r="H14" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1387,7 +1370,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1397,31 +1380,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <f>COUNTIF(F5:F14,"Done")</f>
         <v/>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <f>COUNTIF(F5:F14,"In Progress")</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <f>COUNTIF(F5:F14,"Under Review")</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="23">
         <f>COUNTIF(F5:F14,"Not Started")</f>
         <v/>
       </c>
@@ -1446,7 +1429,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B942"/>
+    <tabColor rgb="00006100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1471,16 +1454,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: booking    |    Priority: P0    |    Overall status: In Progress</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Service: booking    |    Priority: P0    |    Overall status: Done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Quote → HOLD → pay → KYC → signature → CONFIRMED path is coded, with admin assign vehicle/driver and cancel. Self-drive vs with-driver branch after payment. Chauffeur product rules, policy-based cancel, and admin-created bookings are incomplete.</t>
+          <t>Quote → HOLD → pay token → KYC/sign (self-drive) → CONFIRMED. All rental types price from rules (hourly chauffeur, daily others, one-way city-pair fee, tour package). Policy cancel + refund, admin create/re-quote, vehicle/driver guards, NO_SHOW sweeper, Razorpay.js checkout, guest track OTP, socket subscribe.</t>
         </is>
       </c>
     </row>
@@ -1544,15 +1527,15 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/quotes computes days/hours from PricingRule, optional offer, TTL ~20 min.</t>
+          <t>POST /v1/quotes prices by rental type (hourly local chauffeur, daily others, airport hourly ≤8h + wait/night, ONE_WAY city-pair fee, tour package price, outstation driver nights). TTL 20 min. GET /v1/quotes/:id hydrates car/branches.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/quotes · booking.service.ts quote</t>
-        </is>
-      </c>
-      <c r="F5" s="32" t="inlineStr">
+          <t>POST/GET /v1/quotes · booking.service.ts quote</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1562,11 +1545,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>Airport wait/night/one-way extras not auto-added (see module 08).</t>
-        </is>
-      </c>
+      <c r="H5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -1586,7 +1565,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/quotes/:id/apply-offer validates window, cap, per-user.</t>
+          <t>POST /v1/quotes/:id/apply-offer discounts from stored grossPaise (not stacking). Floor = max(₹1, 10% of gross).</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -1594,7 +1573,7 @@
           <t>POST /v1/quotes/:id/apply-offer</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1604,11 +1583,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>No floor-price guard.</t>
-        </is>
-      </c>
+      <c r="H6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -1628,7 +1603,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/bookings creates HOLD, reserves vehicle, moves to AWAITING_PAYMENT or cancels if no car.</t>
+          <t>POST /v1/bookings creates HOLD, copies extras, reserves vehicle in a catalog transaction, moves to AWAITING_PAYMENT or cancels if no car.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1636,7 +1611,7 @@
           <t>POST /v1/bookings</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1670,7 +1645,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/bookings/:id includes history, extras, payments, KYC, agreements, driver, inspections. Owner or staff.</t>
+          <t>GET /v1/bookings/:id includes history, extras, payments/refunds, KYC, agreements, driver, inspections, vehicle, branches. Owner or staff.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -1678,7 +1653,7 @@
           <t>GET /v1/bookings/:id</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1708,7 +1683,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Allowed until HANDOVER/ONGOING/COMPLETED. Releases availability.</t>
+          <t>Allowed until HANDOVER. Hours-before-start policy by rental type writes Refund rows (100/50/0%). Releases availability.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1716,9 +1691,9 @@
           <t>POST /v1/bookings/:id/cancel</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -1728,7 +1703,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>No hours-before-start policy or auto refund.</t>
+          <t>Razorpay refund API is module 06.</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1725,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>TOKEN/BALANCE success → SELF_DRIVE AWAITING_KYC else CONFIRMED. KYC approved → AWAITING_SIGNATURE. Signed → CONFIRMED.</t>
+          <t>TOKEN/BALANCE success → SELF_DRIVE AWAITING_KYC else CONFIRMED. KYC → AWAITING_SIGNATURE. Signed → CONFIRMED. Self-drive handover blocked without KYC+sign. Admin CONFIRMED requires paid token unless comped.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -1758,7 +1733,7 @@
           <t>internal /payment-captured /kyc-approved /agreement-signed</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1770,7 +1745,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>With-driver skips KYC/sign by design.</t>
+          <t>With-driver skips DL KYC/sign by design.</t>
         </is>
       </c>
     </row>
@@ -1792,17 +1767,17 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/admin/bookings, PATCH notes/dates/flight, POST status with confirm/release side effects.</t>
+          <t>List filters status/q/dates. PATCH dates re-quotes and re-reserves. Status POST supports comped. Admin /bookings and /bookings/[id] UI.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> /v1/admin/bookings* · apps/admin/app/bookings</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>/v1/admin/bookings* · apps/admin/app/bookings</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1810,11 +1785,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Date change does not re-quote or re-check availability.</t>
-        </is>
-      </c>
+      <c r="H11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -1834,7 +1805,7 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/admin/bookings/:id/assign-vehicle.</t>
+          <t>Validates same model, AVAILABLE, insurance expiry, overlap via catalog reserve (row lock).</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -1842,9 +1813,9 @@
           <t>POST .../assign-vehicle</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1852,11 +1823,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Does not re-validate insurance/status/overlap.</t>
-        </is>
-      </c>
+      <c r="H12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1876,7 +1843,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>POST assign-driver upserts DriverAssignment.</t>
+          <t>Active, same city as pickup, not on leave, no overlapping CONFIRMED+ trip. Blocked on SELF_DRIVE.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1884,9 +1851,9 @@
           <t>POST .../assign-driver</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1894,11 +1861,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>No one-ongoing-trip or city-match validation.</t>
-        </is>
-      </c>
+      <c r="H13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -1918,7 +1881,7 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>BookingStatusHistory written on create, pay, KYC, sign, cancel, expire, handover, return.</t>
+          <t>BookingStatusHistory written on create, pay, KYC, sign, cancel, expire, no-show, handover, return. Socket emit on each setStatus.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -1926,7 +1889,7 @@
           <t>BookingStatusHistory</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1956,7 +1919,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>/checkout/:quoteId applies offer, creates booking, mock-verifies Razorpay, goes to success.</t>
+          <t>/checkout/:quoteId loads quote, login gate, offer, HOLD, mock verify or Razorpay.js, polls payment, success branches self-drive vs chauffeur.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1964,9 +1927,9 @@
           <t>Checkout.jsx</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1976,7 +1939,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>No live Razorpay.js checkout when mock=false.</t>
+          <t>Live Razorpay still needs keys (module 06).</t>
         </is>
       </c>
     </row>
@@ -1998,17 +1961,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>/track/:bookingId new Track.jsx (old /order-tracking still exists).</t>
+          <t>/track/:bookingId timeline + driver/vehicle. Logged-out: publicId + phone OTP (matches User.phone).</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Track.jsx</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Track.jsx · POST /v1/public/bookings/track/*</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2016,11 +1979,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>Logged-out track-by-phone OTP not built.</t>
-        </is>
-      </c>
+      <c r="H16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -2040,17 +1999,17 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>apps/socket BookingGateway on :4010.</t>
+          <t>API POSTs /internal/booking-status to socket :4010. Web Track + admin detail subscribe (socket.io CDN) with poll fallback.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>apps/socket</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>apps/socket + bookingSocket.js</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -2060,7 +2019,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Web/admin do not subscribe yet.</t>
+          <t>Socket process must be running for live push.</t>
         </is>
       </c>
     </row>
@@ -2082,17 +2041,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>No dedicated sales-create endpoint; would use customer quote APIs.</t>
+          <t>POST /v1/admin/bookings with userId or customerEmail; optional extras, notes, flight, comped (waives token).</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST /v1/admin/bookings</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2100,11 +2059,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>Add POST /v1/admin/bookings with userId.</t>
-        </is>
-      </c>
+      <c r="H18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -2119,22 +2074,22 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Status enum includes NO_SHOW; admin can POST status. No automatic grace job.</t>
+          <t>Worker every 10 min POSTs /internal/bookings/mark-no-show. CONFIRMED/AWAITING_KYC/SIGNATURE past start+2h → NO_SHOW and release.</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>BookingStatus.NO_SHOW</t>
+          <t>NoShowSweeperJob</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -2144,7 +2099,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Add sweeper after start time.</t>
+          <t>Grace hours via NO_SHOW_GRACE_HOURS (default 2).</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2109,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2164,31 +2119,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>COUNTIF(F5:F19,"Done")</f>
         <v/>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <f>COUNTIF(F5:F19,"In Progress")</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>COUNTIF(F5:F19,"Under Review")</f>
         <v/>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <f>COUNTIF(F5:F19,"Not Started")</f>
         <v/>
       </c>
@@ -2213,7 +2168,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E07A3D"/>
+    <tabColor rgb="00F4B942"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2238,16 +2193,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Service: payment    |    Priority: P0    |    Overall status: Under Review</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Service: payment    |    Priority: P0    |    Overall status: In Progress</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Razorpay order + verify + webhook + mock mode, invoices with flat 18% GST, offline pay, refund rows, deposit flags. Live Razorpay, real refunds, state-wise GST, and deposit authorize/capture need review in staging.</t>
+          <t>Razorpay order + verify + webhook + mock mode, state-wise GST invoices (CGST/SGST vs IGST) with generated PDF, offline pay, Razorpay refund API, deposit auto-release on return, full admin UI (payments/invoices/deposits/recon). Settlement recon runs against Razorpay when keys are set, otherwise mock.</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2266,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/payments/orders uses booking amount. Mock order if no RAZORPAY_KEY_ID or PAYMENTS_MOCK=true.</t>
+          <t>POST /v1/payments/orders uses booking amount; BALANCE computes remaining due. Mock order if no RAZORPAY_KEY_ID or PAYMENTS_MOCK=true.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -2319,7 +2274,7 @@
           <t>POST /v1/payments/orders</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2329,11 +2284,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>Amount is booking.amountPaise even for BALANCE (not remaining due).</t>
-        </is>
-      </c>
+      <c r="H5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -2361,7 +2312,7 @@
           <t>POST /v1/payments/verify</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2395,7 +2346,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/webhooks/razorpay signature check + idempotent eventId on captured/authorized.</t>
+          <t>POST /v1/webhooks/razorpay signature check + idempotent eventId on captured/authorized + refund.processed webhook.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2403,7 +2354,7 @@
           <t>POST /v1/webhooks/razorpay</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
@@ -2437,17 +2388,17 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Creates INV-YEAR-##### with GST 18% lines after SUCCESS.</t>
+          <t>Creates INV-YEAR-##### with CGST/SGST vs IGST by state. GET /v1/me/invoices/:id/pdf returns a generated GST PDF. Account + admin download buttons.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>payment.service.ts afterSuccess</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>payment.service.ts afterSuccess · invoice-pdf.ts</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2455,11 +2406,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Not CGST/SGST vs IGST by state; no PDF.</t>
-        </is>
-      </c>
+      <c r="H8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2479,15 +2426,15 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/invoices.</t>
+          <t>GET /v1/me/invoices. Customer /account/invoices page with print/download.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/invoices</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
+          <t>GET /v1/me/invoices · AccountInvoices.jsx</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2497,11 +2444,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>No customer UI yet.</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -2521,7 +2464,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/admin/payments/offline marks SUCCESS and runs afterSuccess + audit.</t>
+          <t>POST /v1/admin/payments/offline marks SUCCESS and runs afterSuccess + audit. Admin UI modal.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -2529,7 +2472,7 @@
           <t>POST /v1/admin/payments/offline</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2563,7 +2506,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/admin/payments/:id/refund writes Refund row and payment status. Does not call Razorpay refund API.</t>
+          <t>POST /v1/admin/payments/:id/refund calls Razorpay refund API for live payments, writes Refund row. Validates max refundable. Admin UI refund modal.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -2571,9 +2514,9 @@
           <t>POST /v1/admin/payments/:id/refund</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -2583,7 +2526,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Wire Razorpay refunds + webhook.</t>
+          <t>Refund webhook updates razorpayRefundId.</t>
         </is>
       </c>
     </row>
@@ -2605,17 +2548,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>POST deposits/:id/capture|release toggles held/released flags.</t>
+          <t>POST deposits/:id/capture|release toggles held/released. Auto-release triggered on fleet return inspection via internal endpoint. Admin UI capture/release buttons.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/admin/deposits/:id/*</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/admin/deposits/:id/* · internal/deposits/release-by-booking</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2625,7 +2568,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>No Razorpay authorize; no auto-release after return inspection.</t>
+          <t>Razorpay authorize not implemented (uses manual capture).</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2632,7 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>apps/admin/app/payments page.</t>
+          <t>Tabbed admin page: payments (refund + offline), invoices (GST + PDF), deposits (capture/release), recon (run settlement match).</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -2697,9 +2640,9 @@
           <t>apps/admin/app/payments/page.jsx</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2707,11 +2650,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Needs refund/deposit actions in UI.</t>
-        </is>
-      </c>
+      <c r="H14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -2731,17 +2670,17 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>No PayoutReconciliation flow.</t>
+          <t>POST /v1/admin/payments/reconcile pulls Razorpay combined settlement report (3 months) or mock-matches when PAYMENTS_MOCK. Upserts PayoutReconciliation (MATCHED/MISMATCH/UNMATCHED_*). Admin Recon tab.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST/GET /v1/admin/payments/reconcile · apps/admin payments Recon tab</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -2751,7 +2690,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Finance mismatch queue.</t>
+          <t>Live recon needs RAZORPAY_KEY_ID + secret; mock mode writes MATCHED/OFFLINE rows.</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2700,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -2771,31 +2710,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>COUNTIF(F5:F15,"Done")</f>
         <v/>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>COUNTIF(F5:F15,"In Progress")</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="22">
         <f>COUNTIF(F5:F15,"Under Review")</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="23">
         <f>COUNTIF(F5:F15,"Not Started")</f>
         <v/>
       </c>
@@ -2926,7 +2865,7 @@
           <t>packages/database/prisma/schema.prisma SubscriptionPlan</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3010,7 +2949,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3048,7 +2987,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3086,7 +3025,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3108,7 +3047,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -3118,31 +3057,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>COUNTIF(F5:F9,"Done")</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>COUNTIF(F5:F9,"In Progress")</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <f>COUNTIF(F5:F9,"Under Review")</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <f>COUNTIF(F5:F9,"Not Started")</f>
         <v/>
       </c>
@@ -3167,488 +3106,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B942"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 — Airport, outstation, one-way &amp; tours</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: booking    |    Priority: P1–P2    |    Overall status: In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Tour packages and city-pair one-way rates have APIs. Quote accepts all RentalType values but pricing is still daily/hourly rules only — no terminal wait slabs, night charges, or driver allowance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Functionality</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Actor</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Implementation (what exists today)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Code / API</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Gaps / next work</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>08.01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Public tour packages</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>GET /v1/public/packages published TourPackage + TourDay.</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>GET /v1/public/packages</t>
-        </is>
-      </c>
-      <c r="F5" s="32" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>No /packages web route.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>08.02</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Admin packages CRUD</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>GET/POST/PATCH + POST delete /v1/admin/packages.</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> /v1/admin/packages</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>No admin UI page; daysDetail not edited on create.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>08.03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>City-pair one-way fee</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>GET/POST /v1/admin/city-pairs upserts CityPairRate.</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> /v1/admin/city-pairs</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>Quote engine does not add oneWayPaise yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>08.04</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Quote product types</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>POST /v1/quotes accepts SELF_DRIVE, WITH_DRIVER_*, AIRPORT, OUTSTATION, ONE_WAY, TOUR, SUBSCRIPTION via Prisma enum.</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>POST /v1/quotes rentalType</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>WITH_DRIVER_LOCAL uses hourlyPaise; others use dailyPaise only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>08.05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Flight number</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>adminPatch can set flightNumber.</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>PATCH /v1/admin/bookings/:id</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Customer checkout does not collect flight/terminal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>08.06</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Airport terminals &amp; wait slabs</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>AirportTerminal model only — no API.</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>schema AirportTerminal</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Free wait minutes + night charges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>08.07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Outstation driver allowance</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Not in quote calculation.</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Auto-add per night.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>08.08</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Web packages page</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Not in Container.jsx routes.</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Add /packages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Counts</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Under Review</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="19">
-        <f>COUNTIF(F5:F12,"Done")</f>
-        <v/>
-      </c>
-      <c r="C15" s="20">
-        <f>COUNTIF(F5:F12,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>COUNTIF(F5:F12,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="E15" s="22">
-        <f>COUNTIF(F5:F12,"Not Started")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:H12"/>
-  <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick Done, In Progress, Under Review, or Not Started" prompt="Status" type="list">
-      <formula1>"Done,In Progress,Under Review,Not Started"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F4B942"/>
+    <tabColor rgb="00006100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3668,21 +3126,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>09 — Legal KYC &amp; documents</t>
+          <t>08 — Airport, outstation, one-way &amp; tours</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: document    |    Priority: P0    |    Overall status: In Progress</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Service: booking + fleet + catalog    |    Priority: P1–P2    |    Overall status: Done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Customer submit + admin approve/reject advances self-drive bookings. Zoho webhook creates a KYC case. Uploads do not issue signed Cloudinary slots. Aadhaar hashing, DL expiry rules, and 12-month reuse are not built.</t>
+          <t>Airport wait/night, outstation driver allowance, one-way city-pair fee, and tour packages are quoted and bookable. Admin /packages configures terminals, city pairs, tours, and nightly allowance. Web /packages lists tours. SALES can add extra km/hours on return.</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3189,12 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>09.01</t>
+          <t>08.01</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Submit KYC case</t>
+          <t>Public tour packages</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -3746,106 +3204,98 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/kyc/submit creates KycCase SUBMITTED + KycDocument URLs; sets profile.kycStatus.</t>
+          <t>GET /v1/public/packages and /:slug return published TourPackage + TourDay + city. Web /packages listing and detail.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/kyc/submit</t>
-        </is>
-      </c>
-      <c r="F5" s="32" t="inlineStr">
+          <t>GET /v1/public/packages · Packages.jsx</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>No MIME/size validation server-side.</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>09.02</t>
+          <t>08.02</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Signed upload slots</t>
+          <t>Admin packages CRUD</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/kyc/uploads echoes url/kind — does not mint Cloudinary/S3 signature.</t>
+          <t>CRUD with days, inclusions, car class, city, itinerary daysDetail. Soft-unpublish via POST delete. Admin /packages tab.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/kyc/uploads</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>/v1/admin/packages · apps/admin/app/packages</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Issue signed upload; never accept arbitrary URLs in prod.</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>09.03</t>
+          <t>08.03</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>My KYC</t>
+          <t>City-pair one-way fee</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Admin / Customer</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/kyc with documents + zoho.</t>
+          <t>GET /v1/public/city-pairs + admin upsert/delete. Quote requires drop city ≠ pickup and a configured pair; fee added to amount.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/kyc · Kyc.jsx</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
+          <t>/v1/admin/city-pairs · quote ONE_WAY</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr"/>
@@ -3853,138 +3303,130 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>09.04</t>
+          <t>08.04</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Admin KYC queue + decision</t>
+          <t>Quote product types</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/kyc; POST decision APPROVED/REJECTED; on approve calls booking kyc-approved.</t>
+          <t>AIRPORT hourly ≤8h + wait/night; OUTSTATION daily + driver nights; ONE_WAY daily + pair fee; TOUR_PACKAGE fixed package price (car class must match).</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> /v1/admin/kyc · apps/admin/app/kyc</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
+          <t>POST /v1/quotes rentalType</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>No UNDER_REVIEW state transition or request-reupload per doc.</t>
+          <t>Wait is a single slab after free minutes, not multi-slab.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>09.05</t>
+          <t>08.05</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Zoho Forms webhook</t>
+          <t>Flight number &amp; terminal</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/webhooks/zoho-form upserts user by email, attaches latest awaiting booking, stores raw ZohoSubmission.</t>
+          <t>Car detail collects terminal, optional flight, wait minutes. Stored on quote payload and Booking.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/webhooks/zoho-form</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>CarDetail.jsx · Booking.flightNumber/terminalId</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>No HMAC; no attachment download to Cloudinary; weak booking match (email+status only).</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>09.06</t>
+          <t>08.06</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Aadhaar / PAN storage policy</t>
+          <t>Airport terminals &amp; wait/night</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Stores whatever URL/notes client sends. No hash+last4.</t>
+          <t>CRUD /v1/admin/airports + GET /v1/public/airports. Free wait minutes, paise/min, night window (IST) and surcharge.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>KycDocument</t>
+          <t>AirportTerminal · fleet airports</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Do not log raw Aadhaar.</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>09.07</t>
+          <t>08.07</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>DL expiry vs drop-off</t>
+          <t>Outstation driver allowance</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -3994,22 +3436,22 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Not validated.</t>
+          <t>CatalogSettings.driverAllowancePerNightPaise × IST midnights crossed, auto-added as a quote extra.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>priceWindow OUTSTATION</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr"/>
@@ -4017,37 +3459,37 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>09.08</t>
+          <t>08.08</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Reusable KYC 12 months</t>
+          <t>Web packages page</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>New case created every submit.</t>
+          <t>/packages and /packages/:slug. Header Tours link. Book → /fleet with packageId + car class.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>apps/web/src/ms/pages/Packages.jsx</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr"/>
@@ -4055,42 +3497,42 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>09.09</t>
+          <t>08.09</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Web KYC UI</t>
+          <t>Extra km / hours on return</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Kyc.jsx on /account/kyc.</t>
+          <t>POST /v1/admin/bookings/:id/extras. SALES may override before return; others only on HANDOVER+.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>apps/web/src/ms/pages/Kyc.jsx</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>addBookingExtras · booking detail UI</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Complete doc kinds + rejection reason display.</t>
+          <t>Does not auto-compute extra km from odometer (handover module).</t>
         </is>
       </c>
     </row>
@@ -4100,7 +3542,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4110,31 +3552,534 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>COUNTIF(F5:F13,"Done")</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <f>COUNTIF(F5:F13,"In Progress")</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="22">
         <f>COUNTIF(F5:F13,"Under Review")</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="23">
+        <f>COUNTIF(F5:F13,"Not Started")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H13"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick Done, In Progress, Under Review, or Not Started" prompt="Status" type="list">
+      <formula1>"Done,In Progress,Under Review,Not Started"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E07A3D"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>09 — Legal KYC &amp; documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Service: document    |    Priority: P0    |    Overall status: Under Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Customer upload (MIME/size) + hashed Aadhaar/PAN last4 + DL vs drop-off + 12-month reuse + admin review/reject/re-upload. Zoho webhook HMAC + attachment pull need staging secrets. Signed Cloudinary slots need API_SECRET; unsigned server upload works today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Implementation (what exists today)</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Code / API</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Gaps / next work</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>09.01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Submit KYC case</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>POST /v1/kyc/submit with docs + optional Aadhaar/PAN/DL expiry. Validates kinds, required self-drive set (DL + Aadhaar/address + selfie), updates REJECTED cases in place.</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>POST /v1/kyc/submit · document.service.ts submitKyc</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>09.02</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Signed upload slots</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>POST /v1/kyc/uploads issues a Cloudinary signed slot when API_KEY+SECRET are set; otherwise returns mode=server. Multipart file is validated (pdf/jpg/png/webp, 8 MB) and uploaded via the API. Production rejects arbitrary URLs.</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>POST /v1/kyc/uploads · lib/cloudinary.ts issueCloudinarySlot</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Set CLOUDINARY_API_KEY + CLOUDINARY_API_SECRET for direct-to-Cloudinary signed uploads. Unsigned preset still used for server-side uploads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>09.03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>My KYC</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>GET /v1/me/kyc returns cases, documents, last4, validUntil, reusable flag. Hashes never leave the API.</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>GET /v1/me/kyc · GET /v1/me/documents</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>09.04</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Admin KYC queue + decision</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>GET /v1/admin/kyc with status filter, DL expiry flags. POST review → UNDER_REVIEW. Decision APPROVED/REJECTED (reason required). Request re-upload per doc. SUPPORT + SUPER_ADMIN decide; SALES view-only. Admin /kyc has doc viewer.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> /v1/admin/kyc · apps/admin/app/kyc</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>No KYC_OFFICER role in RoleName — SUPPORT is the designated KYC role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>09.05</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Zoho Forms webhook</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>POST /v1/webhooks/zoho-form verifies ZOHO_WEBHOOK_SECRET (header or HMAC) in production, upserts user, matches booking by email+dates+car, stores hashed Aadhaar/PAN, strips raw IDs from ZohoSubmission.raw. Downloads attachments to Cloudinary when Zoho OAuth env is set.</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>POST /v1/webhooks/zoho-form · lib/zoho.ts</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Needs ZOHO_WEBHOOK_SECRET in prod. Attachment pull needs ZOHO_CLIENT_ID/SECRET/REFRESH_TOKEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>09.06</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Aadhaar / PAN storage policy</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Raw numbers hashed with KYC_HASH_PEPPER (SHA-256); only last4 stored. Never written to audit logs or Zoho raw JSON.</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>lib/kyc.ts identityStamp · KycCase.aadhaarHash</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Set KYC_HASH_PEPPER in production (falls back to SESSION_SECRET).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>09.07</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>DL expiry vs drop-off</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>DL expiry required on submit; must be after booking.endsAt. Handover also blocks if DL misses drop-off. Admin queue flags expired / expiring / misses-drop-off.</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>submitKyc assertDlCoversDropOff · fleet handover</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>09.08</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Reusable KYC 12 months</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>On approve, validUntil = min(12 months, DL expiry). Payment capture calls /internal/kyc/apply-reusable to clone an approved case onto the new booking and skip AWAITING_KYC.</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>applyReusable · kycValidUntil</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>09.09</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Web KYC UI</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Per-doc file pickers (Aadhaar, PAN, DL, selfie, address), hashed ID fields, DL date, rejection reason, re-upload highlighting, reusable-approved state.</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>apps/web/src/ms/pages/account/AccountKyc.jsx</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="20">
+        <f>COUNTIF(F5:F13,"Done")</f>
+        <v/>
+      </c>
+      <c r="C16" s="21">
+        <f>COUNTIF(F5:F13,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>COUNTIF(F5:F13,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="E16" s="23">
         <f>COUNTIF(F5:F13,"Not Started")</f>
         <v/>
       </c>
@@ -4184,7 +4129,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Service: document    |    Priority: P0    |    Overall status: Under Review</t>
         </is>
@@ -4193,7 +4138,7 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>HTML template render + send envelope (mock without LEEGALITY_API_KEY) + webhook/manual mark-signed advances booking to CONFIRMED. Not a real PDF yet. Vendor integration needs staging review.</t>
+          <t>PDF generate (vehicle, tariff, jurisdiction) + mock/live Leegality send + webhook HMAC/IP + customer PDF download + template CRUD by city/product + void/re-issue. Live eSign still needs a published Leegality workflow and staging credentials.</t>
         </is>
       </c>
     </row>
@@ -4257,17 +4202,17 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/agreements/generate renders HTML placeholders (publicId, customer, dates, amount). pdfUrl is html://…</t>
+          <t>POST /v1/agreements/generate builds a real PDF (parties, vehicle, dates, tariff, deposit, city jurisdiction) from AgreementTemplate HTML. Self-drive requires APPROVED KYC. Reuses an open DRAFT.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/agreements/generate</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/agreements/generate · agreement-pdf.ts · GET /v1/me/agreements/:id/pdf</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -4277,7 +4222,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Replace with PDFKit/HTML→PDF; vehicle + tariff + jurisdiction fields.</t>
+          <t>PDF is Helvetica (same as invoices), not PDFKit. Legal clause copy still needs counsel review.</t>
         </is>
       </c>
     </row>
@@ -4299,15 +4244,15 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/agreements/:id/send-leegality creates SignatureEnvelope. Mock id if no API key; live POST is best-effort.</t>
+          <t>POST /v1/agreements/:id/send-leegality posts v3 /sign/request with profileId + base64 PDF + invitee email matching the customer. Mocks envelope when LEEGALITY_API_KEY or LEEGALITY_PROFILE_ID is missing.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/agreements/:id/send-leegality</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
+          <t>POST /v1/agreements/:id/send-leegality · leegality.ts createLeegalityRequest</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
@@ -4319,7 +4264,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Complete real Leegality payload + invite email match.</t>
+          <t>BLOCKER: published Leegality workflow (LEEGALITY_PROFILE_ID) + API key. Invite emails/SMS are sent by Leegality from the workflow, not by us. Staging review still required.</t>
         </is>
       </c>
     </row>
@@ -4341,17 +4286,17 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/webhooks/leegality updates envelope/agreement; on SIGN calls agreement-signed.</t>
+          <t>POST /v1/webhooks/leegality verifies HMAC-SHA1 mac (documentId + LEEGALITY_PRIVATE_SALT) and optional IP allowlist. Completed → fetch signed file, store SignedArtifact, advance booking.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/webhooks/leegality</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/webhooks/leegality · leegality.ts verifyLeegalityWebhook</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -4361,7 +4306,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Add signature/IP allowlist.</t>
+          <t>BLOCKER: set LEEGALITY_PRIVATE_SALT (required in production). Webhook URL must be configured on the Leegality workflow (cannot set via send API). Set LEEGALITY_IP_ALLOWLIST once vendor IPs are known.</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4328,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/admin/agreements/:id/mark-signed treats as signed.</t>
+          <t>POST /v1/admin/agreements/:id/mark-signed (SUPPORT/SUPER_ADMIN) sets WAIVED, optional wet-ink URL, advances booking like a signed envelope.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -4391,7 +4336,7 @@
           <t>POST /v1/admin/agreements/:id/mark-signed</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4401,11 +4346,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>No void/re-issue endpoint.</t>
-        </is>
-      </c>
+      <c r="H8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -4425,17 +4366,17 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/agreements/:id owner or staff.</t>
+          <t>GET /v1/me/agreements/:id plus authenticated PDF and signed-pdf streams. Account Agreements and booking detail download with the session token.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/agreements/:id</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>GET /v1/me/agreements/:id · /pdf · /signed-pdf</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -4445,7 +4386,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>No signed PDF file yet.</t>
+          <t>Live signed bytes come from Leegality Details API after webhook; mock/waiver stamps the generated PDF.</t>
         </is>
       </c>
     </row>
@@ -4467,17 +4408,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>AgreementTemplate matched by rentalType or null. No admin CRUD.</t>
+          <t>CRUD on AgreementTemplate (name, html, cityId, rentalType, active). Generate picks city+product, then city, then product, then default HTML.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>schema AgreementTemplate</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>GET/POST/PATCH/DELETE /v1/admin/agreement-templates · apps/admin/app/agreements</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -4485,11 +4426,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Add CRUD + city dimension.</t>
-        </is>
-      </c>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -4509,17 +4446,17 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/admin/agreements/:id/void not implemented.</t>
+          <t>POST /v1/admin/agreements/:id/void (SUPER_ADMIN) sets VOID + reason; optional reissue generates a replacement DRAFT and links supersededById.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST /v1/admin/agreements/:id/void</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4527,7 +4464,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKER: void does not recall a live Leegality envelope — cancel that invite in the Leegality dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4535,7 +4476,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4545,31 +4486,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>COUNTIF(F5:F11,"Done")</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>COUNTIF(F5:F11,"In Progress")</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>COUNTIF(F5:F11,"Under Review")</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>COUNTIF(F5:F11,"Not Started")</f>
         <v/>
       </c>
@@ -4594,7 +4535,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B942"/>
+    <tabColor rgb="00006100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4619,16 +4560,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: fleet    |    Priority: P0    |    Overall status: In Progress</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Service: fleet    |    Priority: P0    |    Overall status: Done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Cities, branches, vehicles CRUD and expiry read are live. Vehicle documents (RC/insurance/PUC) have a table but no admin CRUD. Assignment does not yet block on insurance dates.</t>
+          <t>Physical vehicles are distinct from CarModel. CRUD, queued or immediate branch transfer, RC/insurance/PUC files (local upload if no Cloudinary), 30-day expiry emails, partner-contract check, and insurance-covers-booking on assignment.</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4641,7 @@
           <t>GET /v1/public/cities</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4730,15 +4671,15 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH/DELETE /v1/admin/cities.</t>
+          <t>GET/POST/PATCH/DELETE /v1/admin/cities. Vehicles page Cities &amp; branches tab can create cities.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> /v1/admin/cities</t>
-        </is>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
+          <t xml:space="preserve"> /v1/admin/cities · apps/admin/app/vehicles</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4750,7 +4691,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>No admin cities page in Shell.</t>
+          <t>Full city editor (edit/delete) still SUPER_ADMIN/CITY_MANAGER API; tab is create+list.</t>
         </is>
       </c>
     </row>
@@ -4772,15 +4713,15 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH/DELETE /v1/admin/branches?cityId=</t>
+          <t>GET/POST/PATCH/DELETE /v1/admin/branches. Vehicles page can create branches.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> /v1/admin/branches</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
+          <t xml:space="preserve"> /v1/admin/branches · apps/admin/app/vehicles</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4792,7 +4733,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Same — API only in new admin.</t>
+          <t>Edit/delete remain API-only.</t>
         </is>
       </c>
     </row>
@@ -4814,15 +4755,15 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Full CRUD; list includes model, branch, partner. Status/branch/odometer/partner on patch.</t>
+          <t>Full CRUD with model/branch/partner/status/odometer. Unique registration. BRANCH_MANAGER scoped when StaffScope is set. PUT /v1/admin/staff/:id/scope on Customers page.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> /v1/admin/vehicles · apps/admin/app/vehicles</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
+          <t xml:space="preserve"> /v1/admin/vehicles · PUT /v1/admin/staff/:id/scope</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -4832,11 +4773,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Registration unique at DB; no transfer-job entity.</t>
-        </is>
-      </c>
+      <c r="H8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -4856,17 +4793,17 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>PATCH vehicle.branchId (also drop-branch on return).</t>
+          <t>POST transfer-branch immediate (default) or queued job. Pending jobs listed; complete/cancel. Queued transfer blocks AVAILABLE cars until complete.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>PATCH /v1/admin/vehicles/:id</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/admin/vehicles/:id/transfer-branch · /v1/admin/vehicle-transfers</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -4874,11 +4811,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>No POST transfer-branch with audit/task.</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -4898,17 +4831,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/vehicles/expiries — documents expiring in 30 days.</t>
+          <t>GET expiries + POST /v1/admin/vehicles/expiries/notify emails FLEET_OPS/CITY_MANAGER. Worker cron 08:00. alertedAt avoids daily spam.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/vehicles/expiries</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>GET expiries · POST expiries/notify · VehicleExpiryJob</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -4918,7 +4851,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>No VehicleDocument create/update API.</t>
+          <t>Needs GMAIL_USER for real mail; otherwise console mock.</t>
         </is>
       </c>
     </row>
@@ -4940,17 +4873,17 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>VehicleDocument model only.</t>
+          <t>Document CRUD. Local disk upload when Cloudinary is unset (/v1/files/...). POST backfill-documents fills missing RC/insurance/PUC/permit on existing cars. New vehicles get placeholders automatically.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>schema VehicleDocument</t>
+          <t>VehicleDocument · /v1/uploads · backfill-documents</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4958,11 +4891,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>CRUD + insurance-covers-booking check before assign.</t>
-        </is>
-      </c>
+      <c r="H11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -4982,15 +4911,15 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>ownerType/partnerId on create/update.</t>
+          <t>ownerType/partnerId on create/update. Active partner + covering PartnerContract required. POST /v1/admin/partners/:id/contracts from the Vehicles geo tab.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>createVehicle</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
+          <t>createVehicle · assertPartnerContractActive</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5002,7 +4931,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Contract-active check not enforced.</t>
+          <t>Full partner settlement UI is still module 15.</t>
         </is>
       </c>
     </row>
@@ -5012,7 +4941,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5022,31 +4951,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>COUNTIF(F5:F12,"Done")</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>COUNTIF(F5:F12,"In Progress")</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>COUNTIF(F5:F12,"Under Review")</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>COUNTIF(F5:F12,"Not Started")</f>
         <v/>
       </c>
@@ -5177,7 +5106,7 @@
           <t>POST /v1/admin/maintenance-jobs</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5261,7 +5190,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5303,7 +5232,7 @@
           <t>schema MaintenancePart</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5341,7 +5270,7 @@
           <t>schema Workshop</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5379,7 +5308,7 @@
           <t>apps/admin/components/Shell.jsx</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5397,7 +5326,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5407,31 +5336,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>COUNTIF(F5:F10,"Done")</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>COUNTIF(F5:F10,"In Progress")</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>COUNTIF(F5:F10,"Under Review")</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>COUNTIF(F5:F10,"Not Started")</f>
         <v/>
       </c>
@@ -5562,7 +5491,7 @@
           <t>POST /v1/admin/bookings/:id/handover</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5604,7 +5533,7 @@
           <t>POST /v1/admin/bookings/:id/return</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5688,7 +5617,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5726,7 +5655,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5768,7 +5697,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -5828,7 +5757,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5838,31 +5767,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>COUNTIF(F5:F11,"Done")</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>COUNTIF(F5:F11,"In Progress")</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>COUNTIF(F5:F11,"Under Review")</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>COUNTIF(F5:F11,"Not Started")</f>
         <v/>
       </c>
@@ -6116,12 +6045,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Kyc.jsx exists. POST /v1/kyc/submit, GET /v1/me/kyc. Uploads currently send a URL (no signed Cloudinary slot UI).</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Kyc.jsx: per-doc pickers (Aadhaar/PAN/DL/selfie/address), hashed numbers, DL expiry, rejection/re-upload. POST /v1/kyc/uploads (multipart) + POST /v1/kyc/submit + GET /v1/me/kyc.</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -6131,7 +6060,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Per-doc pickers; Cloudinary signed upload; rejection UX.</t>
+          <t>Direct Cloudinary signed upload needs CLOUDINARY_API_SECRET; server upload works now.</t>
         </is>
       </c>
     </row>
@@ -6153,17 +6082,17 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>List agreements per booking. Open Leegality sign link. Download signed PDF when ready. Status DRAFT/SENT/SIGNED.</t>
+          <t>List agreements per booking. Download draft/signed PDF when ready. Status DRAFT/SENT/SIGNED/WAIVED.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>No page. GET /v1/me/agreements/:id is by id only (no list).</t>
+          <t>/account/agreements · AccountAgreements.jsx · GET /v1/me/documents · GET /v1/me/agreements/:id/pdf and /signed-pdf.</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -6173,7 +6102,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Needs list endpoint or derive from booking.agreements; then build UI.</t>
+          <t>Leegality invite/sign URL is on the envelope after send (module 10).</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6129,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>No page. GET /v1/me/invoices returns Invoice + lines. No PDF yet.</t>
+          <t>AccountInvoices.jsx on /account/invoices. GET /v1/me/invoices. Authenticated PDF download via GET /v1/me/invoices/:id/pdf.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -6213,11 +6142,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Build list + print view even if PDF comes later.</t>
-        </is>
-      </c>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -6245,7 +6170,7 @@
           <t>No page. GET /v1/me/wallet exists (balance 0, no debit at checkout).</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -6287,7 +6212,7 @@
           <t>No page. POST /v1/tickets exists. No customer list/reply UI.</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -6329,7 +6254,7 @@
           <t>PATCH /v1/me accepts fullName, phone, address JSON. No form.</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -6351,7 +6276,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6361,31 +6286,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>COUNTIF(F5:F13,"Done")</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <f>COUNTIF(F5:F13,"In Progress")</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="22">
         <f>COUNTIF(F5:F13,"Under Review")</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="23">
         <f>COUNTIF(F5:F13,"Not Started")</f>
         <v/>
       </c>
@@ -6516,7 +6441,7 @@
           <t xml:space="preserve"> /v1/admin/drivers · apps/admin/app/drivers</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6554,7 +6479,7 @@
           <t>POST /v1/admin/bookings/:id/assign-driver</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6638,7 +6563,7 @@
           <t>schema DriverLeave</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -6676,7 +6601,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -6694,7 +6619,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6704,31 +6629,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>COUNTIF(F5:F9,"Done")</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>COUNTIF(F5:F9,"In Progress")</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <f>COUNTIF(F5:F9,"Under Review")</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <f>COUNTIF(F5:F9,"Not Started")</f>
         <v/>
       </c>
@@ -6859,7 +6784,7 @@
           <t xml:space="preserve"> /v1/admin/partners</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6897,7 +6822,7 @@
           <t>PUT .../commission-rules</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6939,7 +6864,7 @@
           <t>POST /internal/ledger/trip-complete</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6981,7 +6906,7 @@
           <t>GET .../ledger</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7019,7 +6944,7 @@
           <t>POST /v1/admin/settlements/generate</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7103,7 +7028,7 @@
           <t>README Out of scope</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -7125,7 +7050,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7135,31 +7060,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>COUNTIF(F5:F11,"Done")</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>COUNTIF(F5:F11,"In Progress")</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>COUNTIF(F5:F11,"Under Review")</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>COUNTIF(F5:F11,"Not Started")</f>
         <v/>
       </c>
@@ -7218,7 +7143,7 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>New ops console (port 3001) has dashboard, bookings, cars, vehicles, drivers, KYC, customers, payments, partners, leads, offers, CMS, reports. City/Branch exist on entities. StaffScope table exists but there is no assign-scope API or query filtering. Old admin UI still lives inside apps/web /admin.</t>
+          <t>Ops console (port 3001) has a city/branch switcher, dedicated /cities and /staff pages, and dashboard KPIs (handovers, overdue returns, KYC, signatures, failed payments, workshop). Bookings, vehicles, drivers, KYC, agreements, payments, tickets, and maintenance honor StaffScope plus the switcher. Legacy apps/web /admin is still present.</t>
         </is>
       </c>
     </row>
@@ -7282,17 +7207,17 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Next.js apps/admin with sidebar nav + token gate.</t>
+          <t>Next.js apps/admin with sidebar, token gate, city/branch switcher, /cities and /staff routes.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>apps/admin/components/Shell.jsx</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>apps/admin/components/Shell.jsx · /cities · /staff</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -7302,7 +7227,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Missing cities/branches/staff/maintenance/inspections/tickets/notifications pages.</t>
+          <t>Inspections stay on booking detail. Notification-template admin page is still missing.</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7249,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/dashboard: bookings count, pending KYC, free vehicles, revenue, byStatus.</t>
+          <t>GET /v1/admin/dashboard scoped by location: bookings, pending KYC, free vehicles, revenue, today’s handovers, overdue returns, pending signatures, failed payments, workshop, byStatus. Optional from/to.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7332,9 +7257,9 @@
           <t>GET /v1/admin/dashboard · app/page.jsx</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -7342,11 +7267,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Spec also wants today’s handovers, overdue returns, pending signatures, failed payments, workshop — not included.</t>
-        </is>
-      </c>
+      <c r="H6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -7374,7 +7295,7 @@
           <t>schema City Branch</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7404,17 +7325,17 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>StaffScope model. PUT /v1/admin/staff/:id/scope not implemented.</t>
+          <t>PUT /v1/admin/staff/:id/scope. Dedicated /staff page plus Customers invite.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>schema StaffScope</t>
+          <t>PUT /v1/admin/staff/:id/scope · app/staff</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -7422,11 +7343,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>CITY_MANAGER / BRANCH_MANAGER filtering.</t>
-        </is>
-      </c>
+      <c r="H8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -7446,17 +7363,17 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Lists return all rows; SUPER_ADMIN bypass only on roles.</t>
+          <t>x-ops-city-id / x-ops-branch-id overlay for SUPER_ADMIN and CITY_MANAGER. Bookings, vehicles, drivers, KYC, agreements, payments, tickets, maintenance, dashboard filter by pickup branch / vehicle branch.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>lib/auth.ts</t>
+          <t>vehicleScopeWhere · bookingScopeWhere · AuthMiddleware</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -7464,11 +7381,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Filter bookings/vehicles by x-city-id / x-branch-id.</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -7518,7 +7431,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7528,31 +7441,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>COUNTIF(F5:F10,"Done")</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>COUNTIF(F5:F10,"In Progress")</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>COUNTIF(F5:F10,"Under Review")</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>COUNTIF(F5:F10,"Not Started")</f>
         <v/>
       </c>
@@ -7767,7 +7680,7 @@
           <t>docs/api-routes.md</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -7805,7 +7718,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -7885,7 +7798,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -7903,7 +7816,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -7913,31 +7826,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>COUNTIF(F5:F10,"Done")</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>COUNTIF(F5:F10,"In Progress")</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>COUNTIF(F5:F10,"Under Review")</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>COUNTIF(F5:F10,"Not Started")</f>
         <v/>
       </c>
@@ -8110,7 +8023,7 @@
           <t>POST /v1/quotes/:id/apply-offer</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8194,7 +8107,7 @@
           <t>schema LoyaltyAccount</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -8232,7 +8145,7 @@
           <t>schema Referral</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -8254,7 +8167,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8264,31 +8177,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>COUNTIF(F5:F9,"Done")</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>COUNTIF(F5:F9,"In Progress")</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <f>COUNTIF(F5:F9,"Under Review")</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <f>COUNTIF(F5:F9,"Not Started")</f>
         <v/>
       </c>
@@ -8503,7 +8416,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -8541,7 +8454,7 @@
           <t>POST /v1/tickets</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8605,7 +8518,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8615,31 +8528,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>COUNTIF(F5:F9,"Done")</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>COUNTIF(F5:F9,"In Progress")</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <f>COUNTIF(F5:F9,"Under Review")</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <f>COUNTIF(F5:F9,"Not Started")</f>
         <v/>
       </c>
@@ -8689,7 +8602,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Service: notification + worker    |    Priority: P0    |    Overall status: Under Review</t>
         </is>
@@ -8770,7 +8683,7 @@
           <t>POST /internal/notify · notify.service.ts</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8812,7 +8725,7 @@
           <t>notify.service.ts deliver</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
@@ -8938,7 +8851,7 @@
           <t xml:space="preserve"> /v1/admin/notification-templates</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -8980,7 +8893,7 @@
           <t>GET /v1/admin/notifications</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9064,7 +8977,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9082,7 +8995,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9092,31 +9005,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>COUNTIF(F5:F12,"Done")</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>COUNTIF(F5:F12,"In Progress")</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>COUNTIF(F5:F12,"Under Review")</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>COUNTIF(F5:F12,"Not Started")</f>
         <v/>
       </c>
@@ -9247,7 +9160,7 @@
           <t>POST /v1/public/leads · POST /v1/public/contact</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9289,7 +9202,7 @@
           <t>GET /v1/admin/leads</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9327,7 +9240,7 @@
           <t>PATCH /v1/admin/leads/:id</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9369,7 +9282,7 @@
           <t>POST .../notes</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9407,7 +9320,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9449,7 +9362,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9491,7 +9404,7 @@
           <t>WhatsAppPopup.jsx</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9509,7 +9422,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9519,31 +9432,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>COUNTIF(F5:F11,"Done")</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>COUNTIF(F5:F11,"In Progress")</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>COUNTIF(F5:F11,"Under Review")</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>COUNTIF(F5:F11,"Not Started")</f>
         <v/>
       </c>
@@ -9716,7 +9629,7 @@
           <t>App.tsx</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9758,7 +9671,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9800,7 +9713,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9838,7 +9751,7 @@
           <t>POST /v1/me/devices</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9880,7 +9793,7 @@
           <t>apps/mobile/package.json</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -9902,7 +9815,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -9912,31 +9825,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>COUNTIF(F5:F10,"Done")</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>COUNTIF(F5:F10,"In Progress")</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>COUNTIF(F5:F10,"Under Review")</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>COUNTIF(F5:F10,"Not Started")</f>
         <v/>
       </c>
@@ -10232,12 +10145,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Checkout.jsx applies offer, POST /v1/bookings, POST /v1/payments/orders, mock-verifies, then success. No quote GET (uses id from URL only).</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Checkout.jsx loads GET /v1/quotes/:id, offer, login gate, HOLD, mock or Razorpay.js, polls payment.</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -10247,7 +10160,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Load quote details; login redirect; do not mock-verify when Razorpay keys exist.</t>
+          <t>Live Razorpay needs keys (module 06).</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10177,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>/checkout/pay</t>
+          <t>/checkout/:quoteId</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -10274,12 +10187,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>No /checkout/pay route. Checkout.jsx verifies immediately when order.mock is true.</t>
+          <t>Razorpay Checkout.js opens when order.mock is false; verify + poll GET /v1/payments/:id. Mock path still verifies immediately.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -10289,7 +10202,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Add Razorpay.js checkout page; poll payment status; never trust client success alone.</t>
+          <t>Needs RAZORPAY_KEY_ID in API env for the live widget.</t>
         </is>
       </c>
     </row>
@@ -10316,12 +10229,12 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>SuccessMs.jsx exists after mock pay.</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>SuccessMs.jsx loads booking, self-drive vs chauffeur copy, links to KYC/track/account.</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -10329,11 +10242,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Poll payment; branch copy for self-drive vs chauffeur.</t>
-        </is>
-      </c>
+      <c r="H11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -10353,17 +10262,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Timeline: HOLD → payment → KYC → signature → confirmed → handover → ongoing → return → completed. Logged-in users use GET /v1/bookings/:id. Logged-out: id + phone OTP (later). Show driver name after assignment.</t>
+          <t>Timeline: HOLD → payment → KYC → signature → confirmed → handover → ongoing → return → completed. Logged-in users use GET /v1/bookings/:id. Logged-out: id + phone OTP. Show driver name after assignment.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Track.jsx on /track/:bookingId. Old /order-tracking still exists. Guest OTP not built.</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Track.jsx timeline, driver/vehicle, socket subscribe. Guest: publicId + phone OTP.</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -10373,7 +10282,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Guest track; live status via socket :4010 optional.</t>
+          <t>OTP is emailed via notify template; SMS later.</t>
         </is>
       </c>
     </row>
@@ -10516,22 +10425,22 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>/packages</t>
+          <t>/packages  /packages/:slug</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>List published tour/airport packages with days, price, inclusions. Select → quote with product AIRPORT/TOUR.</t>
+          <t>List published tour packages with days, price, inclusions. Detail shows itinerary. CTA goes to /fleet with TOUR_PACKAGE + packageId + car class.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>No route in Container.jsx. GET /v1/public/packages is ready.</t>
+          <t>Packages.jsx listing + detail. Header Tours link. CarDetail collects airport terminal/flight/wait, outstation km, one-way drop branch, tour package.</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -10539,11 +10448,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>Build listing + detail after daily booking path is stable.</t>
-        </is>
-      </c>
+      <c r="H16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -10613,7 +10518,7 @@
           <t>Testimonial.jsx + TestimonialContext (old). No new API.</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -10635,7 +10540,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -10645,31 +10550,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>COUNTIF(F5:F18,"Done")</f>
         <v/>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <f>COUNTIF(F5:F18,"In Progress")</f>
         <v/>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <f>COUNTIF(F5:F18,"Under Review")</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <f>COUNTIF(F5:F18,"Not Started")</f>
         <v/>
       </c>
@@ -10698,7 +10603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10839,12 +10744,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>app/page.jsx shows bookings, pending KYC, vehicles free, revenue, byStatus. GET /v1/admin/dashboard.</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>app/page.jsx KPI cards including handovers, overdue returns, KYC, signatures, failed payments, workshop, free vehicles, bookings, revenue. Date filter + shell city/branch.</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -10852,11 +10757,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Add remaining KPIs when API returns them; city filter.</t>
-        </is>
-      </c>
+      <c r="H6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -10881,12 +10782,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>app/bookings/page.jsx exists (list).</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>List with status/q filters, create-on-behalf form, row links to detail. GET /v1/admin/bookings.</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -10894,11 +10795,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>Filters + pagination; status chips.</t>
-        </is>
-      </c>
+      <c r="H7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -10923,12 +10820,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>No [id] page. APIs: GET booking, PATCH, POST status/assign-vehicle/assign-driver, POST handover/return, agreements, offline pay.</t>
+          <t>apps/admin/app/bookings/[id]: timeline, re-quote dates, assign vehicle/driver, status+comped, policy cancel. Socket subscribe.</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -10938,7 +10835,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Highest-value admin screen after list. Build this next.</t>
+          <t>Handover/return photo capture still lives as API actions / module 13.</t>
         </is>
       </c>
     </row>
@@ -11002,17 +10899,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>CRUD physical cars: registration, model, branch, status, odometer, partner. Expiry alerts for RC/insurance/PUC.</t>
+          <t>CRUD physical cars: registration, model, branch, status, odometer, partner. Queue or immediate branch transfer. RC/insurance/PUC/permit upload (local files if no Cloudinary) + expiry emails. Backfill missing docs. Partner contract required for partner cars.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>app/vehicles/page.jsx + /v1/admin/vehicles. GET expiries exists, no document CRUD UI.</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>app/vehicles/page.jsx — Fleet / Expiries / Cities &amp; branches. transfer-branch, vehicle-transfers complete/cancel, documents CRUD, expiries/notify, backfill-documents.</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -11020,11 +10917,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Status change; branch transfer; document expiry panel.</t>
-        </is>
-      </c>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -11052,7 +10945,7 @@
           <t>No page. Availability is computed in catalog search.</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11091,7 +10984,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>app/customers/page.jsx + GET /v1/admin/users, PATCH roles, POST disable.</t>
+          <t>app/customers/page.jsx + GET /v1/admin/users, PATCH roles, PUT /v1/admin/staff/:id/scope, POST disable. Invite sets city/branch.</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -11106,7 +10999,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Customer drawer with bookings + KYC; role editor.</t>
+          <t>Customer drawer with bookings + KYC.</t>
         </is>
       </c>
     </row>
@@ -11133,12 +11026,12 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>app/kyc/page.jsx + GET /v1/admin/kyc, POST .../decision.</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>app/kyc/page.jsx: status filter, doc viewer, reject reason required, per-doc re-upload, UNDER_REVIEW, DL expiry flags. GET /v1/admin/kyc + POST decision/review/request-reupload.</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -11148,7 +11041,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Doc viewer; reject reason required.</t>
+          <t>SALES is view-only; SUPPORT/SUPER_ADMIN decide.</t>
         </is>
       </c>
     </row>
@@ -11170,17 +11063,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>List envelopes. Generate PDF, send Leegality, mark signed (waiver), void/re-issue later.</t>
+          <t>List envelopes. Generate PDF, send Leegality, mark signed (waiver), void/re-issue. Templates by city/product.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>No admin page. APIs: generate, send-leegality, mark-signed.</t>
+          <t>app/agreements/page.jsx + Shell. GET /v1/admin/agreements, generate/send/mark-signed/void, template CRUD. Booking detail has Generate.</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -11190,7 +11083,7 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Can also live as actions on booking detail for MVP.</t>
+          <t>Live Leegality still needs workflow credentials (module 10).</t>
         </is>
       </c>
     </row>
@@ -11217,12 +11110,12 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>app/payments/page.jsx only. Refund/deposit/offline APIs exist without dedicated UI.</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Tabbed page: payments (refund/offline), invoices (GST + PDF), deposits (capture/release), recon (run Razorpay settlement match). GET /v1/admin/payments|invoices|deposits + POST /v1/admin/payments/reconcile.</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -11230,11 +11123,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>Add refund + offline + deposit actions; invoices tab.</t>
-        </is>
-      </c>
+      <c r="H15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
@@ -11304,7 +11193,7 @@
           <t>No Shell link. POST /v1/admin/maintenance-jobs exists.</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11346,7 +11235,7 @@
           <t>No page. POST /v1/admin/bookings/:id/handover and /return.</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11427,12 +11316,12 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>No pages. City/branch APIs exist. StaffScope assign API missing.</t>
+          <t>app/cities/page.jsx + app/staff/page.jsx. Shell city/branch switcher sends x-ops-city-id / x-ops-branch-id. PUT /v1/admin/staff/:id/scope.</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -11440,11 +11329,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>Cities/branches UI can ship before staff-scope API.</t>
-        </is>
-      </c>
+      <c r="H20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -11598,7 +11483,7 @@
           <t>No Shell links. GET /v1/admin/tickets and /reviews exist. No PATCH moderate.</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11682,7 +11567,7 @@
           <t>No page. GET logs + PUT templates exist.</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11698,60 +11583,98 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>FE.AD.23</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Trips, tours &amp; airports</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>/packages</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Tabs: tour package CRUD (days/inclusions/class), city-pair one-way fees, airport terminals (wait + night), outstation driver-allowance policy. Booking detail can add extra km/hours.</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>app/packages/page.jsx + Shell Trips &amp; tours. Booking extras on /bookings/[id].</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="19">
-        <f>COUNTIF(F5:F26,"Done")</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f>COUNTIF(F5:F26,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f>COUNTIF(F5:F26,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="E29" s="22">
-        <f>COUNTIF(F5:F26,"Not Started")</f>
+    <row r="30">
+      <c r="B30" s="20">
+        <f>COUNTIF(F5:F27,"Done")</f>
+        <v/>
+      </c>
+      <c r="C30" s="21">
+        <f>COUNTIF(F5:F27,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>COUNTIF(F5:F27,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="E30" s="23">
+        <f>COUNTIF(F5:F27,"Not Started")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H26"/>
+  <autoFilter ref="A4:H27"/>
   <mergeCells count="3">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick Done, In Progress, Under Review, or Not Started" prompt="Status" type="list">
+    <dataValidation sqref="F5:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick Done, In Progress, Under Review, or Not Started" prompt="Status" type="list">
       <formula1>"Done,In Progress,Under Review,Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11869,7 +11792,7 @@
           <t>Not built.</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11911,7 +11834,7 @@
           <t>Dev token only (Bearer dev:email) on App.tsx.</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -11995,7 +11918,7 @@
           <t>Not built (name + price only on list).</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -12033,7 +11956,7 @@
           <t>Not built.</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -12075,7 +11998,7 @@
           <t>Not built.</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -12155,7 +12078,7 @@
           <t>Not built.</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -12173,7 +12096,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -12183,31 +12106,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>COUNTIF(F5:F12,"Done")</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>COUNTIF(F5:F12,"In Progress")</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>COUNTIF(F5:F12,"Under Review")</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>COUNTIF(F5:F12,"Not Started")</f>
         <v/>
       </c>
@@ -12330,50 +12253,50 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>FE Web Account</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>apps/web :3000</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <f>COUNTIF('FE Web Account'!F:F,"Done")</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="24">
         <f>COUNTIF('FE Web Account'!F:F,"In Progress")</f>
         <v/>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="24">
         <f>COUNTIF('FE Web Account'!F:F,"Under Review")</f>
         <v/>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="24">
         <f>COUNTIF('FE Web Account'!F:F,"Not Started")</f>
         <v/>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="24">
         <f>F5+G5+H5+I5</f>
         <v/>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="26">
         <f>IF(J5=0,0,F5/J5)</f>
         <v/>
       </c>
@@ -12384,50 +12307,50 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>FE Web Public</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>apps/web :3000</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>P0–P1</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>COUNTIF('FE Web Public'!F:F,"Done")</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>COUNTIF('FE Web Public'!F:F,"In Progress")</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <f>COUNTIF('FE Web Public'!F:F,"Under Review")</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <f>COUNTIF('FE Web Public'!F:F,"Not Started")</f>
         <v/>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="27">
         <f>F6+G6+H6+I6</f>
         <v/>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="28">
         <f>IF(J6=0,0,F6/J6)</f>
         <v/>
       </c>
@@ -12438,50 +12361,50 @@
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>FE Admin</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>apps/admin</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>P0–P1</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>COUNTIF('FE Admin'!F:F,"Done")</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f>COUNTIF('FE Admin'!F:F,"In Progress")</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="24">
         <f>COUNTIF('FE Admin'!F:F,"Under Review")</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="24">
         <f>COUNTIF('FE Admin'!F:F,"Not Started")</f>
         <v/>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="24">
         <f>F7+G7+H7+I7</f>
         <v/>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <f>IF(J7=0,0,F7/J7)</f>
         <v/>
       </c>
@@ -12492,50 +12415,50 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>FE Mobile</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>apps/mobile</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>COUNTIF('FE Mobile'!F:F,"Done")</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>COUNTIF('FE Mobile'!F:F,"In Progress")</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>COUNTIF('FE Mobile'!F:F,"Under Review")</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>COUNTIF('FE Mobile'!F:F,"Not Started")</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>F8+G8+H8+I8</f>
         <v/>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="28">
         <f>IF(J8=0,0,F8/J8)</f>
         <v/>
       </c>
@@ -12546,1184 +12469,1184 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>01 Auth &amp; Security</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>identity (apps/api)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F9" s="24">
+        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G9" s="24">
+        <f>COUNTIF('01 Auth &amp; Security'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H9" s="24">
+        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I9" s="24">
+        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J9" s="24">
+        <f>F9+G9+H9+I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="26">
+        <f>IF(J9=0,0,F9/J9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Firebase + Postgres user sync, OTP (Postgres 5-min TTL), session mint, roles, last-super-admin lock, staff invite, audit+IP, CORS allowlist. Google button shows when NEXT_PUBLIC_GOOGLE_CLIENT_ID is set. Staff city/branch list filters live in module 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>02 Public CMS</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>platform + apps/web</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F9" s="23">
-        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G9" s="23">
-        <f>COUNTIF('01 Auth &amp; Security'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H9" s="23">
-        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I9" s="23">
-        <f>COUNTIF('01 Auth &amp; Security'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J9" s="23">
-        <f>F9+G9+H9+I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="25">
-        <f>IF(J9=0,0,F9/J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Firebase + Postgres user sync, OTP, roles, and audit exist. OTP is in-memory (not Redis). Google login and last-super-admin lock are not built. Staff city/branch scope is stored but not fully enforced on every list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>02 Public CMS</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>platform + apps/web</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="F10" s="27">
+        <f>COUNTIF('02 Public CMS'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>COUNTIF('02 Public CMS'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H10" s="27">
+        <f>COUNTIF('02 Public CMS'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I10" s="27">
+        <f>COUNTIF('02 Public CMS'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J10" s="27">
+        <f>F10+G10+H10+I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="28">
+        <f>IF(J10=0,0,F10/J10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>Ported marketing site still runs in Next.js (home, blogs, monsoon bar). New CMS APIs exist for pages, banners, blogs, contact. Admin CMS page is a first version. Testimonials/comments still largely on the old UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>03 Customer Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>identity + booking + payment + document + web</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F11" s="24">
+        <f>COUNTIF('03 Customer Dashboard'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>COUNTIF('03 Customer Dashboard'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>COUNTIF('03 Customer Dashboard'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>COUNTIF('03 Customer Dashboard'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J11" s="24">
+        <f>F11+G11+H11+I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="26">
+        <f>IF(J11=0,0,F11/J11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Logged-in /account lists bookings and KYC status. APIs exist for invoices, wallet, tickets, agreements-by-id. Dedicated screens for invoices/wallet/tickets/agreements are not built yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>04 Search &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F12" s="27">
+        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>COUNTIF('04 Search &amp; Availability'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J12" s="27">
+        <f>F12+G12+H12+I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>IF(J12=0,0,F12/J12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>Public search, car detail calendar, availability, seasonal pricing, buffer settings, vehicle blocks, HOLD reserve/release/confirm with a serializable lock, and the worker HOLD sweeper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>05 Booking Engine</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F13" s="24">
+        <f>COUNTIF('05 Booking Engine'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>COUNTIF('05 Booking Engine'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>COUNTIF('05 Booking Engine'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>COUNTIF('05 Booking Engine'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>F13+G13+H13+I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="26">
+        <f>IF(J13=0,0,F13/J13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>Quote → HOLD → pay token → KYC/sign (self-drive) → CONFIRMED. All rental types price from rules (hourly chauffeur, daily others, one-way city-pair fee, tour package). Policy cancel + refund, admin create/re-quote, vehicle/driver guards, NO_SHOW sweeper, Razorpay.js checkout, guest track OTP, socket subscribe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>06 Payments</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F14" s="27">
+        <f>COUNTIF('06 Payments'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G14" s="27">
+        <f>COUNTIF('06 Payments'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>COUNTIF('06 Payments'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I14" s="27">
+        <f>COUNTIF('06 Payments'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J14" s="27">
+        <f>F14+G14+H14+I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="28">
+        <f>IF(J14=0,0,F14/J14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>Razorpay order + verify + webhook + mock mode, state-wise GST invoices (CGST/SGST vs IGST) with generated PDF, offline pay, Razorpay refund API, deposit auto-release on return, full admin UI (payments/invoices/deposits/recon). Settlement recon runs against Razorpay when keys are set, otherwise mock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>07 Subscription</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>booking + catalog</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F15" s="24">
+        <f>COUNTIF('07 Subscription'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G15" s="24">
+        <f>COUNTIF('07 Subscription'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H15" s="24">
+        <f>COUNTIF('07 Subscription'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I15" s="24">
+        <f>COUNTIF('07 Subscription'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J15" s="24">
+        <f>F15+G15+H15+I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="26">
+        <f>IF(J15=0,0,F15/J15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>Data model + POST /v1/subscriptions creates a SUBSCRIPTION booking from a plan. No public plans API, swap, pause, or recurring invoices. After-MVP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>08 Airport &amp; Packages</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>booking + fleet + catalog</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>P1–P2</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F16" s="27">
+        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
+        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I16" s="27">
+        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J16" s="27">
+        <f>F16+G16+H16+I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="28">
+        <f>IF(J16=0,0,F16/J16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>Airport wait/night, outstation driver allowance, one-way city-pair fee, and tour packages are quoted and bookable. Admin /packages configures terminals, city pairs, tours, and nightly allowance. Web /packages lists tours. SALES can add extra km/hours on return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>09 KYC &amp; Documents</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="F17" s="24">
+        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G17" s="24">
+        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H17" s="24">
+        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I17" s="24">
+        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J17" s="24">
+        <f>F17+G17+H17+I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="26">
+        <f>IF(J17=0,0,F17/J17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>Customer upload (MIME/size) + hashed Aadhaar/PAN last4 + DL vs drop-off + 12-month reuse + admin review/reject/re-upload. Zoho webhook HMAC + attachment pull need staging secrets. Signed Cloudinary slots need API_SECRET; unsigned server upload works today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>10 Agreement &amp; eSign</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="F18" s="27">
+        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G18" s="27">
+        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H18" s="27">
+        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I18" s="27">
+        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J18" s="27">
+        <f>F18+G18+H18+I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="28">
+        <f>IF(J18=0,0,F18/J18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>PDF generate (vehicle, tariff, jurisdiction) + mock/live Leegality send + webhook HMAC/IP + customer PDF download + template CRUD by city/product + void/re-issue. Live eSign still needs a published Leegality workflow and staging credentials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>11 Fleet</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>fleet</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F19" s="24">
+        <f>COUNTIF('11 Fleet'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G19" s="24">
+        <f>COUNTIF('11 Fleet'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H19" s="24">
+        <f>COUNTIF('11 Fleet'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I19" s="24">
+        <f>COUNTIF('11 Fleet'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J19" s="24">
+        <f>F19+G19+H19+I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="26">
+        <f>IF(J19=0,0,F19/J19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>Physical vehicles are distinct from CarModel. CRUD, queued or immediate branch transfer, RC/insurance/PUC files (local upload if no Cloudinary), 30-day expiry emails, partner-contract check, and insurance-covers-booking on assignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>12 Maintenance</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>fleet</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F20" s="27">
+        <f>COUNTIF('12 Maintenance'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G20" s="27">
+        <f>COUNTIF('12 Maintenance'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H20" s="27">
+        <f>COUNTIF('12 Maintenance'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I20" s="27">
+        <f>COUNTIF('12 Maintenance'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J20" s="27">
+        <f>F20+G20+H20+I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="28">
+        <f>IF(J20=0,0,F20/J20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>Creating a maintenance job writes an availability block so search will not sell that car. Complete-job, parts, workshop CRUD, and admin UI are not built. After-MVP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>13 Handover &amp; Return</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>fleet</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F10" s="26">
-        <f>COUNTIF('02 Public CMS'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G10" s="26">
-        <f>COUNTIF('02 Public CMS'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H10" s="26">
-        <f>COUNTIF('02 Public CMS'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I10" s="26">
-        <f>COUNTIF('02 Public CMS'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J10" s="26">
-        <f>F10+G10+H10+I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="27">
-        <f>IF(J10=0,0,F10/J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>Ported marketing site still runs in Next.js (home, blogs, monsoon bar). New CMS APIs exist for pages, banners, blogs, contact. Admin CMS page is a first version. Testimonials/comments still largely on the old UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>03 Customer Dashboard</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>identity + booking + payment + document + web</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="F21" s="24">
+        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>COUNTIF('13 Handover &amp; Return'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H21" s="24">
+        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I21" s="24">
+        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J21" s="24">
+        <f>F21+G21+H21+I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="26">
+        <f>IF(J21=0,0,F21/J21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>Minimal handover/return APIs store odometer, fuel, photos, damages and move booking ONGOING → COMPLETED. Vehicle returns to drop branch and partner ledger is posted. Deposit auto-release and full damage matrix are not done. Delivery-exec app is out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>14 Drivers</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>fleet</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F22" s="27">
+        <f>COUNTIF('14 Drivers'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G22" s="27">
+        <f>COUNTIF('14 Drivers'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H22" s="27">
+        <f>COUNTIF('14 Drivers'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I22" s="27">
+        <f>COUNTIF('14 Drivers'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J22" s="27">
+        <f>F22+G22+H22+I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="28">
+        <f>IF(J22=0,0,F22/J22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>Driver CRUD + assign-to-booking work. Leave, availability calendar, DL validity, and single-assignment rules are not enforced. No driver marketplace (by design).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>15 Partners</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F23" s="24">
+        <f>COUNTIF('15 Partners'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>COUNTIF('15 Partners'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H23" s="24">
+        <f>COUNTIF('15 Partners'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I23" s="24">
+        <f>COUNTIF('15 Partners'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J23" s="24">
+        <f>F23+G23+H23+I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="26">
+        <f>IF(J23=0,0,F23/J23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>Admin-only partner CRUD, commission rules, ledger on trip complete, settlement generate + mark-paid. No partner portal (confirmed exclusion). Open-damage hold and frozen-at-booking commission version still missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>16 Admin &amp; Multi-city</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>fleet + platform + apps/admin</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>P0–P1</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F24" s="27">
+        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G24" s="27">
+        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I24" s="27">
+        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J24" s="27">
+        <f>F24+G24+H24+I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="28">
+        <f>IF(J24=0,0,F24/J24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>Ops console (port 3001) has a city/branch switcher, dedicated /cities and /staff pages, and dashboard KPIs (handovers, overdue returns, KYC, signatures, failed payments, workshop). Bookings, vehicles, drivers, KYC, agreements, payments, tickets, and maintenance honor StaffScope plus the switcher. Legacy apps/web /admin is still present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>17 Finance &amp; Reports</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>platform + payment</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F25" s="24">
+        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>F25+G25+H25+I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="26">
+        <f>IF(J25=0,0,F25/J25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>Basic revenue + GST report endpoints and an admin reports page. No CSV export, deposit/partner reports, or Razorpay recon queue. GST is a flat 18% on invoice create.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>18 Offers &amp; Wallet</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>platform + payment + booking</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>P1–P2</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F26" s="27">
+        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G26" s="27">
+        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H26" s="27">
+        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I26" s="27">
+        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J26" s="27">
+        <f>F26+G26+H26+I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="28">
+        <f>IF(J26=0,0,F26/J26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>Coupon apply on quote is real (window, max redemptions, one per user). Admin can create offers. Wallet/loyalty rows are created at signup but earn/redeem/referral are not. P1 = coupons; P2 = wallet/loyalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>19 Reviews &amp; Support</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F27" s="24">
+        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G27" s="24">
+        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H27" s="24">
+        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I27" s="24">
+        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J27" s="24">
+        <f>F27+G27+H27+I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="26">
+        <f>IF(J27=0,0,F27/J27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>Customers can create a review (unpublished) and a ticket. Admin can list both. No moderate/publish, public car reviews, ticket assign/SLA, or customer ticket UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>20 Notifications</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>notification + worker</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="F28" s="27">
+        <f>COUNTIF('20 Notifications'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G28" s="27">
+        <f>COUNTIF('20 Notifications'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H28" s="27">
+        <f>COUNTIF('20 Notifications'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I28" s="27">
+        <f>COUNTIF('20 Notifications'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J28" s="27">
+        <f>F28+G28+H28+I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="28">
+        <f>IF(J28=0,0,F28/J28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>Internal notify + templates + logs + retry cron. Gmail OAuth/app-password when env is set; otherwise console mock. OTP and booking_confirmed are wired. SMS/WhatsApp later. Staging review once Gmail env is present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>21 CRM &amp; Leads</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F11" s="23">
-        <f>COUNTIF('03 Customer Dashboard'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G11" s="23">
-        <f>COUNTIF('03 Customer Dashboard'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H11" s="23">
-        <f>COUNTIF('03 Customer Dashboard'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I11" s="23">
-        <f>COUNTIF('03 Customer Dashboard'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J11" s="23">
-        <f>F11+G11+H11+I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="25">
-        <f>IF(J11=0,0,F11/J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>Logged-in /account lists bookings and KYC status. APIs exist for invoices, wallet, tickets, agreements-by-id. Dedicated screens for invoices/wallet/tickets/agreements are not built yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>04 Search &amp; Availability</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>catalog</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="F29" s="24">
+        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Done")</f>
+        <v/>
+      </c>
+      <c r="G29" s="24">
+        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="H29" s="24">
+        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Under Review")</f>
+        <v/>
+      </c>
+      <c r="I29" s="24">
+        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Not Started")</f>
+        <v/>
+      </c>
+      <c r="J29" s="24">
+        <f>F29+G29+H29+I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="26">
+        <f>IF(J29=0,0,F29/J29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>Contact and public lead APIs + admin pipeline (NEW→LOST) + notes. Convert-to-booking and 7-day dedupe are not built. Admin /leads page exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>22 Mobile</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>apps/mobile</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F12" s="26">
-        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>COUNTIF('04 Search &amp; Availability'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H12" s="26">
-        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
-        <f>COUNTIF('04 Search &amp; Availability'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J12" s="26">
-        <f>F12+G12+H12+I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="27">
-        <f>IF(J12=0,0,F12/J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>Public search, car detail, availability, pricing CRUD, HOLD reserve/release/confirm, and the worker HOLD sweeper are implemented. Search UI is /fleet. Seasonal pricing and a hard DB lock against double-book are still open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>05 Booking Engine</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F13" s="23">
-        <f>COUNTIF('05 Booking Engine'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G13" s="23">
-        <f>COUNTIF('05 Booking Engine'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H13" s="23">
-        <f>COUNTIF('05 Booking Engine'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I13" s="23">
-        <f>COUNTIF('05 Booking Engine'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J13" s="23">
-        <f>F13+G13+H13+I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="25">
-        <f>IF(J13=0,0,F13/J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>Quote → HOLD → pay → KYC → signature → CONFIRMED path is coded, with admin assign vehicle/driver and cancel. Self-drive vs with-driver branch after payment. Chauffeur product rules, policy-based cancel, and admin-created bookings are incomplete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>06 Payments</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>Under Review</t>
-        </is>
-      </c>
-      <c r="F14" s="26">
-        <f>COUNTIF('06 Payments'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G14" s="26">
-        <f>COUNTIF('06 Payments'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H14" s="26">
-        <f>COUNTIF('06 Payments'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I14" s="26">
-        <f>COUNTIF('06 Payments'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J14" s="26">
-        <f>F14+G14+H14+I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="27">
-        <f>IF(J14=0,0,F14/J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>Razorpay order + verify + webhook + mock mode, invoices with flat 18% GST, offline pay, refund rows, deposit flags. Live Razorpay, real refunds, state-wise GST, and deposit authorize/capture need review in staging.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>07 Subscription</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>booking + catalog</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F15" s="23">
-        <f>COUNTIF('07 Subscription'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G15" s="23">
-        <f>COUNTIF('07 Subscription'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H15" s="23">
-        <f>COUNTIF('07 Subscription'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I15" s="23">
-        <f>COUNTIF('07 Subscription'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J15" s="23">
-        <f>F15+G15+H15+I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="25">
-        <f>IF(J15=0,0,F15/J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>Data model + POST /v1/subscriptions creates a SUBSCRIPTION booking from a plan. No public plans API, swap, pause, or recurring invoices. After-MVP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>08 Airport &amp; Packages</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>P1–P2</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F16" s="26">
-        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G16" s="26">
-        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H16" s="26">
-        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I16" s="26">
-        <f>COUNTIF('08 Airport &amp; Packages'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J16" s="26">
-        <f>F16+G16+H16+I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="27">
-        <f>IF(J16=0,0,F16/J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>Tour packages and city-pair one-way rates have APIs. Quote accepts all RentalType values but pricing is still daily/hourly rules only — no terminal wait slabs, night charges, or driver allowance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>09 KYC &amp; Documents</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F17" s="23">
-        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G17" s="23">
-        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H17" s="23">
-        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I17" s="23">
-        <f>COUNTIF('09 KYC &amp; Documents'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J17" s="23">
-        <f>F17+G17+H17+I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="25">
-        <f>IF(J17=0,0,F17/J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>Customer submit + admin approve/reject advances self-drive bookings. Zoho webhook creates a KYC case. Uploads do not issue signed Cloudinary slots. Aadhaar hashing, DL expiry rules, and 12-month reuse are not built.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>10 Agreement &amp; eSign</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>Under Review</t>
-        </is>
-      </c>
-      <c r="F18" s="26">
-        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
-        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I18" s="26">
-        <f>COUNTIF('10 Agreement &amp; eSign'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J18" s="26">
-        <f>F18+G18+H18+I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="27">
-        <f>IF(J18=0,0,F18/J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="14" t="inlineStr">
-        <is>
-          <t>HTML template render + send envelope (mock without LEEGALITY_API_KEY) + webhook/manual mark-signed advances booking to CONFIRMED. Not a real PDF yet. Vendor integration needs staging review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>11 Fleet</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>fleet</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F19" s="23">
-        <f>COUNTIF('11 Fleet'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G19" s="23">
-        <f>COUNTIF('11 Fleet'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H19" s="23">
-        <f>COUNTIF('11 Fleet'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I19" s="23">
-        <f>COUNTIF('11 Fleet'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J19" s="23">
-        <f>F19+G19+H19+I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
-        <f>IF(J19=0,0,F19/J19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>Cities, branches, vehicles CRUD and expiry read are live. Vehicle documents (RC/insurance/PUC) have a table but no admin CRUD. Assignment does not yet block on insurance dates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>12 Maintenance</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>fleet</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F20" s="26">
-        <f>COUNTIF('12 Maintenance'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G20" s="26">
-        <f>COUNTIF('12 Maintenance'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H20" s="26">
-        <f>COUNTIF('12 Maintenance'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I20" s="26">
-        <f>COUNTIF('12 Maintenance'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J20" s="26">
-        <f>F20+G20+H20+I20</f>
-        <v/>
-      </c>
-      <c r="K20" s="27">
-        <f>IF(J20=0,0,F20/J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="14" t="inlineStr">
-        <is>
-          <t>Creating a maintenance job writes an availability block so search will not sell that car. Complete-job, parts, workshop CRUD, and admin UI are not built. After-MVP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>13 Handover &amp; Return</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>fleet</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F21" s="23">
-        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G21" s="23">
-        <f>COUNTIF('13 Handover &amp; Return'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H21" s="23">
-        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I21" s="23">
-        <f>COUNTIF('13 Handover &amp; Return'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J21" s="23">
-        <f>F21+G21+H21+I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="25">
-        <f>IF(J21=0,0,F21/J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>Minimal handover/return APIs store odometer, fuel, photos, damages and move booking ONGOING → COMPLETED. Vehicle returns to drop branch and partner ledger is posted. Deposit auto-release and full damage matrix are not done. Delivery-exec app is out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>14 Drivers</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>fleet</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F22" s="26">
-        <f>COUNTIF('14 Drivers'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G22" s="26">
-        <f>COUNTIF('14 Drivers'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H22" s="26">
-        <f>COUNTIF('14 Drivers'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I22" s="26">
-        <f>COUNTIF('14 Drivers'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J22" s="26">
-        <f>F22+G22+H22+I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="27">
-        <f>IF(J22=0,0,F22/J22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="14" t="inlineStr">
-        <is>
-          <t>Driver CRUD + assign-to-booking work. Leave, availability calendar, DL validity, and single-assignment rules are not enforced. No driver marketplace (by design).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>15 Partners</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F23" s="23">
-        <f>COUNTIF('15 Partners'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G23" s="23">
-        <f>COUNTIF('15 Partners'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H23" s="23">
-        <f>COUNTIF('15 Partners'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I23" s="23">
-        <f>COUNTIF('15 Partners'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J23" s="23">
-        <f>F23+G23+H23+I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="25">
-        <f>IF(J23=0,0,F23/J23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>Admin-only partner CRUD, commission rules, ledger on trip complete, settlement generate + mark-paid. No partner portal (confirmed exclusion). Open-damage hold and frozen-at-booking commission version still missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>16 Admin &amp; Multi-city</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>fleet + platform + apps/admin</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>P0–P1</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F24" s="26">
-        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G24" s="26">
-        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H24" s="26">
-        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I24" s="26">
-        <f>COUNTIF('16 Admin &amp; Multi-city'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J24" s="26">
-        <f>F24+G24+H24+I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="27">
-        <f>IF(J24=0,0,F24/J24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>New ops console (port 3001) has dashboard, bookings, cars, vehicles, drivers, KYC, customers, payments, partners, leads, offers, CMS, reports. City/Branch exist on entities. StaffScope table exists but there is no assign-scope API or query filtering. Old admin UI still lives inside apps/web /admin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>17 Finance &amp; Reports</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>platform + payment</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F25" s="23">
-        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G25" s="23">
-        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H25" s="23">
-        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I25" s="23">
-        <f>COUNTIF('17 Finance &amp; Reports'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J25" s="23">
-        <f>F25+G25+H25+I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="25">
-        <f>IF(J25=0,0,F25/J25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>Basic revenue + GST report endpoints and an admin reports page. No CSV export, deposit/partner reports, or Razorpay recon queue. GST is a flat 18% on invoice create.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>18 Offers &amp; Wallet</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>platform + payment + booking</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>P1–P2</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F26" s="26">
-        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G26" s="26">
-        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H26" s="26">
-        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I26" s="26">
-        <f>COUNTIF('18 Offers &amp; Wallet'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J26" s="26">
-        <f>F26+G26+H26+I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="27">
-        <f>IF(J26=0,0,F26/J26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>Coupon apply on quote is real (window, max redemptions, one per user). Admin can create offers. Wallet/loyalty rows are created at signup but earn/redeem/referral are not. P1 = coupons; P2 = wallet/loyalty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>19 Reviews &amp; Support</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F27" s="23">
-        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G27" s="23">
-        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H27" s="23">
-        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I27" s="23">
-        <f>COUNTIF('19 Reviews &amp; Support'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J27" s="23">
-        <f>F27+G27+H27+I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="25">
-        <f>IF(J27=0,0,F27/J27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>Customers can create a review (unpublished) and a ticket. Admin can list both. No moderate/publish, public car reviews, ticket assign/SLA, or customer ticket UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>20 Notifications</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>notification + worker</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>Under Review</t>
-        </is>
-      </c>
-      <c r="F28" s="26">
-        <f>COUNTIF('20 Notifications'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G28" s="26">
-        <f>COUNTIF('20 Notifications'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H28" s="26">
-        <f>COUNTIF('20 Notifications'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I28" s="26">
-        <f>COUNTIF('20 Notifications'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J28" s="26">
-        <f>F28+G28+H28+I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="27">
-        <f>IF(J28=0,0,F28/J28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="14" t="inlineStr">
-        <is>
-          <t>Internal notify + templates + logs + retry cron. Gmail OAuth/app-password when env is set; otherwise console mock. OTP and booking_confirmed are wired. SMS/WhatsApp later. Staging review once Gmail env is present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>21 CRM &amp; Leads</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F29" s="23">
-        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Done")</f>
-        <v/>
-      </c>
-      <c r="G29" s="23">
-        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="H29" s="23">
-        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Under Review")</f>
-        <v/>
-      </c>
-      <c r="I29" s="23">
-        <f>COUNTIF('21 CRM &amp; Leads'!F:F,"Not Started")</f>
-        <v/>
-      </c>
-      <c r="J29" s="23">
-        <f>F29+G29+H29+I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="25">
-        <f>IF(J29=0,0,F29/J29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>Contact and public lead APIs + admin pipeline (NEW→LOST) + notes. Convert-to-booking and 7-day dedupe are not built. Admin /leads page exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>22 Mobile</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>apps/mobile</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F30" s="26">
+      <c r="F30" s="27">
         <f>COUNTIF('22 Mobile'!F:F,"Done")</f>
         <v/>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="27">
         <f>COUNTIF('22 Mobile'!F:F,"In Progress")</f>
         <v/>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="27">
         <f>COUNTIF('22 Mobile'!F:F,"Under Review")</f>
         <v/>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="27">
         <f>COUNTIF('22 Mobile'!F:F,"Not Started")</f>
         <v/>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="27">
         <f>F30+G30+H30+I30</f>
         <v/>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="28">
         <f>IF(J30=0,0,F30/J30)</f>
         <v/>
       </c>
@@ -13739,27 +13662,27 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="31">
         <f>SUM(F5:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="31">
         <f>SUM(G5:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="31">
         <f>SUM(H5:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="31">
         <f>SUM(I5:I30)</f>
         <v/>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="31">
         <f>SUM(J5:J30)</f>
         <v/>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="32">
         <f>IF(J31=0,0,F31/J31)</f>
         <v/>
       </c>
@@ -13846,7 +13769,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F4B942"/>
+    <tabColor rgb="00006100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13871,16 +13794,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Service: identity (apps/api)    |    Priority: P0    |    Overall status: In Progress</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Service: identity (apps/api)    |    Priority: P0    |    Overall status: Done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Firebase + Postgres user sync, OTP, roles, and audit exist. OTP is in-memory (not Redis). Google login and last-super-admin lock are not built. Staff city/branch scope is stored but not fully enforced on every list.</t>
+          <t>Firebase + Postgres user sync, OTP (Postgres 5-min TTL), session mint, roles, last-super-admin lock, staff invite, audit+IP, CORS allowlist. Google button shows when NEXT_PUBLIC_GOOGLE_CLIENT_ID is set. Staff city/branch list filters live in module 16.</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13867,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>API verifies Firebase ID tokens with firebase-admin when FIREBASE_PROJECT_ID is set; otherwise token resolve returns null.</t>
+          <t>Verifies Firebase ID tokens via firebase-admin, with Google tokeninfo fallback. Project ID is enough for ID-token verify.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -13952,9 +13875,9 @@
           <t>apps/api/src/auth.middleware.ts → verifyFirebase</t>
         </is>
       </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Under Review</t>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -13964,7 +13887,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Needs staging check with live Firebase project keys.</t>
+          <t>Confirm Firebase authorized domains before prod.</t>
         </is>
       </c>
     </row>
@@ -13986,15 +13909,15 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Bearer dev:email upserts a user and is allowed unless DEV_AUTH_BYPASS=false.</t>
+          <t>Bearer dev:email upserts a user unless NODE_ENV=production or DEV_AUTH_BYPASS=false.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>auth.middleware.ts resolveUser</t>
-        </is>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
+          <t>auth.middleware.ts resolveUser · session-token.ts allowDevAuthBypass</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14028,7 +13951,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/auth/sync upserts User + CustomerProfile + CUSTOMER role + empty wallet/loyalty.</t>
+          <t>POST /v1/auth/sync upserts User + CustomerProfile + CUSTOMER role + empty wallet/loyalty. Disabled accounts are rejected.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -14036,7 +13959,7 @@
           <t>POST /v1/auth/sync · identity.service.ts upsertFromIdentity</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14070,17 +13993,17 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/auth/otp/send issues a 5-min code (in-memory Map) and calls notification service. Dev returns devCode.</t>
+          <t>POST /v1/auth/otp/send stores a hashed 5-min code in EmailOtp (Postgres) and emails via notification service. Dev returns devCode.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>POST /v1/auth/otp/send</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/auth/otp/send · EmailOtp</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -14090,7 +14013,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Replace Map with Redis; production must not expose devCode.</t>
+          <t>Production must not expose devCode (already gated on NODE_ENV).</t>
         </is>
       </c>
     </row>
@@ -14112,17 +14035,17 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/auth/otp/verify checks in-memory store.</t>
+          <t>POST /v1/auth/otp/verify checks hash, upserts user, mints HMAC session token (dd1.*).</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/auth/otp/verify</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST /v1/auth/otp/verify · session-token.ts</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -14130,11 +14053,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>No session mint beyond Firebase; OTP is email-verify helper only.</t>
-        </is>
-      </c>
+      <c r="H9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -14154,15 +14073,15 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>8 requests / 15 minutes per IP on /v1/auth/otp/send.</t>
+          <t>3 requests / 15 minutes per IP and per email. 5 verify attempts then lock.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>auth.middleware.ts rateLimitOtp</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
+          <t>auth.middleware.ts rateLimitOtp · EmailOtp.windowCount</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14172,11 +14091,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Raise to documented 3/15 min if product wants stricter.</t>
-        </is>
-      </c>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -14204,7 +14119,7 @@
           <t>GET/PATCH /v1/me</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14246,7 +14161,7 @@
           <t>POST /v1/me/devices</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14280,7 +14195,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/admin/users?q= for SUPPORT/SALES/CITY_MANAGER/SUPER_ADMIN.</t>
+          <t>GET /v1/admin/users?q=&amp;take= for SUPPORT/SALES/CITY_MANAGER/SUPER_ADMIN. Admin /customers search + role editor.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -14288,7 +14203,7 @@
           <t>GET /v1/admin/users · admin /customers</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14298,11 +14213,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>No pagination beyond simple query.</t>
-        </is>
-      </c>
+      <c r="H13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -14322,15 +14233,15 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>PATCH /v1/admin/users/:id/roles (SUPER_ADMIN).</t>
+          <t>PATCH /v1/admin/users/:id/roles and POST /v1/admin/users/invite. Last remaining SUPER_ADMIN cannot be removed.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>PATCH /v1/admin/users/:id/roles</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
+          <t>PATCH .../roles · POST .../invite</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14340,11 +14251,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Last remaining SUPER_ADMIN cannot be removed — not coded.</t>
-        </is>
-      </c>
+      <c r="H14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -14364,7 +14271,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>POST /v1/admin/users/:id/disable.</t>
+          <t>POST /v1/admin/users/:id/disable. Cannot disable self or the last SUPER_ADMIN. Disabled users cannot authenticate.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -14372,7 +14279,7 @@
           <t>POST /v1/admin/users/:id/disable</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14402,17 +14309,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/audit. Writes happen on auth.sync, role change, disable, offline payment.</t>
+          <t>GET /v1/admin/audit + admin /audit. Identity writes: sync, login, register, google, otp, roles, invite, disable (with IP).</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GET /v1/admin/audit · AuditLog model</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>GET /v1/admin/audit · AuditLog · apps/admin/app/audit</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -14422,7 +14329,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Not every privileged write is audited (refunds, KYC decision, status moves).</t>
+          <t>Refunds/KYC/status audits belong to those modules.</t>
         </is>
       </c>
     </row>
@@ -14444,15 +14351,15 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>requireRoles / requireStaff / assertInternal / assertOwnerOrStaff. SUPER_ADMIN bypasses role checks.</t>
+          <t>requireRoles / requireStaff / assertInternal / assertOwnerOrStaff. CUSTOMER cannot hit /v1/admin. SUPER_ADMIN bypasses role checks.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>apps/api/src/lib/auth.ts</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
+          <t>apps/api/src/lib/auth.ts · auth.middleware.ts</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14464,7 +14371,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>StaffScope (city/branch) is not applied as a query filter.</t>
+          <t>StaffScope (city/branch) query filters are module 16.</t>
         </is>
       </c>
     </row>
@@ -14486,15 +14393,15 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Public: /v1/public/*, OTP, webhooks. Other /v1 requires Bearer.</t>
+          <t>Public: /v1/public/*, OTP, login, register, google, webhooks. Other /v1 requires Bearer. CORS allowlist + security headers.</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>auth.middleware.ts PUBLIC</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr">
+          <t>auth.middleware.ts PUBLIC · main.ts CORS</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14528,7 +14435,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>New login page uses Firebase/dev token via AuthContext.</t>
+          <t>/login supports password, email OTP session, register, optional Google, and local dev token. Header Account/Sign in. Sign-out on /account.</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -14536,9 +14443,9 @@
           <t>apps/web/src/ms/pages/Login.jsx · AuthContext.jsx</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -14548,7 +14455,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Google social login not started.</t>
+          <t>Google button needs NEXT_PUBLIC_GOOGLE_CLIENT_ID.</t>
         </is>
       </c>
     </row>
@@ -14570,17 +14477,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>apps/admin login stores dd_token and calls API.</t>
+          <t>Staff email/password or local mock. Rejects CUSTOMER-only. Sign out in shell.</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>apps/admin/app/login/page.jsx</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>apps/admin/app/login/page.jsx · Shell.jsx</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -14588,11 +14495,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>Uses same Bearer scheme; polish UX later.</t>
-        </is>
-      </c>
+      <c r="H20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -14612,17 +14515,17 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Documented as later; no provider wiring.</t>
+          <t>POST /v1/auth/google verifies Google/Firebase ID token and mints a session. Web GIS button when client id is set.</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>docs/modules/01-auth-security.md</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+          <t>POST /v1/auth/google · Login.jsx</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -14632,7 +14535,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Add Firebase Google provider after email path is stable.</t>
+          <t>Set NEXT_PUBLIC_GOOGLE_CLIENT_ID + GOOGLE_OAUTH_CLIENT_ID to enable the button.</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14545,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14652,31 +14555,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <f>COUNTIF(F5:F21,"Done")</f>
         <v/>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="21">
         <f>COUNTIF(F5:F21,"In Progress")</f>
         <v/>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <f>COUNTIF(F5:F21,"Under Review")</f>
         <v/>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <f>COUNTIF(F5:F21,"Not Started")</f>
         <v/>
       </c>
@@ -14849,7 +14752,7 @@
           <t>GET /v1/public/pages/:slug</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14891,7 +14794,7 @@
           <t>GET /v1/public/banners</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -14975,7 +14878,7 @@
           <t>POST /v1/public/contact</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -15101,7 +15004,7 @@
           <t>schema Testimonial · apps/web Testimonial.jsx</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -15143,7 +15046,7 @@
           <t>schema BlogComment</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -15249,7 +15152,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -15259,31 +15162,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>COUNTIF(F5:F15,"Done")</f>
         <v/>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>COUNTIF(F5:F15,"In Progress")</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="22">
         <f>COUNTIF(F5:F15,"Under Review")</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="23">
         <f>COUNTIF(F5:F15,"Not Started")</f>
         <v/>
       </c>
@@ -15456,7 +15359,7 @@
           <t>GET /v1/me/bookings</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -15490,17 +15393,17 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>/account/kyc page + GET /v1/me/kyc.</t>
+          <t>/account/kyc uploads Aadhaar/PAN/DL/selfie/address, hashed ID numbers, DL expiry, rejection/re-upload UX. GET /v1/me/kyc.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Kyc.jsx · GET /v1/me/kyc</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>Kyc.jsx · GET /v1/me/kyc · POST /v1/kyc/uploads</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -15510,7 +15413,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>See module 09 for upload/signed-URL gaps.</t>
+          <t>Signed Cloudinary slots need CLOUDINARY_API_SECRET (server multipart works without it).</t>
         </is>
       </c>
     </row>
@@ -15658,17 +15561,17 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/agreements/:id by id only — no list endpoint or page.</t>
+          <t>/account/agreements lists status; authenticated PDF and signed-pdf download. GET /v1/me/documents and GET /v1/me/agreements/:id.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>GET /v1/me/agreements/:id</t>
+          <t>AccountAgreements.jsx · GET /v1/me/agreements/:id/pdf</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -15678,7 +15581,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Add GET /v1/me/agreements and /account/agreements.</t>
+          <t>Live signed file from Leegality is module 10.</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15611,7 @@
           <t>docs/modules/03-customer-dashboard.md</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -15730,7 +15633,7 @@
           <t>Counts</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -15740,31 +15643,31 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>Under Review</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <f>COUNTIF(F5:F12,"Done")</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>COUNTIF(F5:F12,"In Progress")</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>COUNTIF(F5:F12,"Under Review")</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>COUNTIF(F5:F12,"Not Started")</f>
         <v/>
       </c>
